--- a/raporlar/2026-10-24/2026-10-24_finans_tablosu.xlsx
+++ b/raporlar/2026-10-24/2026-10-24_finans_tablosu.xlsx
@@ -721,61 +721,61 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9685.4</v>
+        <v>11117</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.42</v>
+        <v>-0.92</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>282.54</v>
+        <v>223.73</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-17.91</v>
+        <v>-32.9</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10.89</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>296.8</v>
+        <v>296.06</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>44.6</v>
+        <v>25.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5842.5</v>
+        <v>7623.68</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.48</v>
+        <v>-0.52</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2738.5</v>
+        <v>4007.9</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3018.45</v>
+        <v>6402.74</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>33.85</v>
+        <v>53.71</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>37.31</v>
+        <v>85.8</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>34.28</v>
+        <v>49.69</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>37.15</v>
+        <v>55.67</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1.0835</v>
+        <v>1.12</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>104.25</v>
+        <v>101.81</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>4.21</v>
+        <v>4.99</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>42.65</v>
@@ -787,43 +787,43 @@
         <v>266.5</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>68450</v>
+        <v>80390.37</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>2640</v>
+        <v>2335.29</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.542</v>
+        <v>1.28</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>57.45</v>
+        <v>59.57</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>116.72</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>4.38</v>
+        <v>6.48</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>TI2 (%3.42)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>IIH (%84.5)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -934,46 +934,46 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9685.4</v>
+        <v>11117</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>puan</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>+1.42% (Artış)</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>+3.85% (Artış)</t>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>-0.92% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>-5.16% (Azalış)</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>-1.90% (Azalış)</t>
+          <t>-13.74% (Azalış)</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>-10.45% (Azalış)</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>+29.65% (Artış)</t>
+          <t>-18.78% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>-1.28% (Azalış)</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>+24.80% (Artış)</t>
+          <t>+4.80% (Artış)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Ana Endeks</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -994,46 +994,46 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10720.15</v>
+        <v>13874.2</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>puan</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>+1.65% (Artış)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>+4.10% (Artış)</t>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>-0.98% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>-4.70% (Azalış)</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>-1.40% (Azalış)</t>
+          <t>-12.96% (Azalış)</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>-9.80% (Azalış)</t>
+          <t>-10.47% (Azalış)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>+33.40% (Artış)</t>
+          <t>+13.50% (Artış)</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>+28.10% (Artış)</t>
+          <t>+19.94% (Artış)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Büyük Ölçekli</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1054,46 +1054,46 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13450</v>
+        <v>15107.2</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>puan</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+2.18% (Artış)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>+5.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>+1.25% (Artış)</t>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>-1.58% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>-4.47% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>-7.12% (Azalış)</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>-8.20% (Azalış)</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>+54.20% (Artış)</t>
+          <t>-2.14% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>-8.66% (Azalış)</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>+61.50% (Artış)</t>
+          <t>+7.21% (Artış)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Bankacılık</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1114,46 +1114,46 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12940.5</v>
+        <v>13562</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>puan</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+0.82% (Artış)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>+2.15% (Artış)</t>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>-1.69% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>-8.47% (Azalış)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>-3.40% (Azalış)</t>
+          <t>-21.67% (Azalış)</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>-14.10% (Azalış)</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>+11.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>+9.40% (Artış)</t>
+          <t>-27.76% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>-3.22% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>-1.34% (Azalış)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Sanayi</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1174,46 +1174,46 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5842.5</v>
+        <v>7623.68</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>puan</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+0.48% (Artış)</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>+0.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>+2.35% (Artış)</t>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>-0.52% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>-0.47% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>-1.04% (Azalış)</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>+7.60% (Artış)</t>
+          <t>+2.84% (Artış)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>+22.40% (Artış)</t>
+          <t>+11.37% (Artış)</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>+38.20% (Artış)</t>
+          <t>+12.25% (Artış)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>ABD Geniş Piyasa</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1234,46 +1234,46 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18590.2</v>
+        <v>25955.34</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>puan</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+0.76% (Artış)</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>+1.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>+3.10% (Artış)</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-0.21% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>-0.71% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>-3.65% (Azalış)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>+8.90% (Artış)</t>
+          <t>+4.10% (Artış)</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>+23.80% (Artış)</t>
+          <t>+11.67% (Artış)</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>+42.10% (Artış)</t>
+          <t>+11.85% (Artış)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>ABD Teknoloji</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>42374.3</v>
+        <v>52215.16</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>-0.32% (Azalış)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>-0.95% (Azalış)</t>
+          <t>-1.23% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>+0.41% (Artış)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>+0.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>+5.40% (Artış)</t>
+          <t>+1.68% (Artış)</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>+0.01% (Yatay)</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>+12.40% (Artış)</t>
+          <t>+8.64% (Artış)</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>+27.60% (Artış)</t>
+          <t>+10.61% (Artış)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>ABD Sanayi</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1354,46 +1354,46 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>18.45</v>
+        <v>19.45</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>puan</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-3.20% (Azalış)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>+2.30% (Artış)</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+2.21% (Artış)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-2.70% (Azalış)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>+19.80% (Artış)</t>
+          <t>+24.12% (Artış)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>+12.10% (Artış)</t>
+          <t>+6.81% (Artış)</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>+48.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>-4.10% (Azalış)</t>
+          <t>+30.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>+12.43% (Artış)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Korku Endeksi</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1414,46 +1414,46 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2738.5</v>
+        <v>4007.9</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+0.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>+1.72% (Artış)</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>+4.30% (Artış)</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>+14.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>+32.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>+38.60% (Artış)</t>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>-1.29% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>-4.14% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>-6.75% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>-1.69% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>-7.68% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>-3.14% (Azalış)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Kıymetli Maden</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1474,46 +1474,46 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>33.85</v>
+        <v>53.71</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+1.15% (Artış)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>+6.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>+9.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>+16.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>+41.20% (Artış)</t>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-1.92% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>-5.76% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>-15.36% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>-8.14% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>-23.42% (Azalış)</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>+46.80% (Artış)</t>
+          <t>+11.03% (Artış)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Kıymetli Maden</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1534,46 +1534,46 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>68450</v>
+        <v>80390.37</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+1.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>+3.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>+8.90% (Artış)</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-0.84% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>-1.79% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>-5.16% (Azalış)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>+4.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>+61.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>+98.40% (Artış)</t>
+          <t>+4.29% (Artış)</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>-8.13% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>-27.60% (Azalış)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Lider Kripto</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1594,46 +1594,46 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2640</v>
+        <v>2335.29</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+0.95% (Artış)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>+1.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>+2.10% (Artış)</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-2.05% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-2.89% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>-13.10% (Azalış)</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>-18.40% (Azalış)</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>+15.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>+44.20% (Artış)</t>
+          <t>-3.67% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>-21.29% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>-40.65% (Azalış)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Akıllı Kontrat</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1654,46 +1654,46 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.542</v>
+        <v>1.28</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+1.50% (Artış)</t>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-0.71% (Azalış)</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>-1.20% (Azalış)</t>
+          <t>-1.38% (Azalış)</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>-6.40% (Azalış)</t>
+          <t>-13.58% (Azalış)</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>-8.90% (Azalış)</t>
+          <t>-12.23% (Azalış)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>-11.80% (Azalış)</t>
+          <t>-30.18% (Azalış)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>-1.40% (Azalış)</t>
+          <t>-48.77% (Azalış)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Ödeme Ağı</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1714,46 +1714,46 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34.28</v>
+        <v>49.69</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>TL</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+0.12% (Artış)</t>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>-0.08% (Yatay)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>+0.32% (Artış)</t>
+          <t>+0.33% (Artış)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>+0.56% (Artış)</t>
+          <t>+1.51% (Artış)</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>+3.88% (Artış)</t>
+          <t>+4.87% (Artış)</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>+16.05% (Artış)</t>
+          <t>+15.68% (Artış)</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>+22.40% (Artış)</t>
+          <t>+18.37% (Artış)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Kur</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1774,46 +1774,46 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>37.15</v>
+        <v>55.67</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>TL</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+0.25% (Artış)</t>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-0.32% (Azalış)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>-0.18% (Yatay)</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>-2.10% (Azalış)</t>
+          <t>+0.16% (Yatay)</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>-0.03% (Yatay)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>+3.40% (Artış)</t>
+          <t>+3.20% (Artış)</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>+13.80% (Artış)</t>
+          <t>+10.02% (Artış)</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>+24.90% (Artış)</t>
+          <t>+13.98% (Artış)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Kur</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1834,46 +1834,46 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.0835</v>
+        <v>1.12</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+0.14% (Artış)</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>-0.45% (Azalış)</t>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-0.15% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>-0.19% (Yatay)</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>-2.65% (Azalış)</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>-0.40% (Yatay)</t>
+          <t>-1.50% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>-1.60% (Azalış)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>-1.95% (Azalış)</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>+2.10% (Artış)</t>
+          <t>-4.62% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>-3.48% (Azalış)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Majör Parite</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>104.25</v>
+        <v>101.81</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1903,37 +1903,37 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>+0.14% (Artış)</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>+0.65% (Artış)</t>
+          <t>+0.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>-0.03% (Yatay)</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>+3.40% (Artış)</t>
+          <t>+0.51% (Artış)</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>-0.15% (Yatay)</t>
+          <t>+0.30% (Yatay)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>+2.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>-1.90% (Azalış)</t>
+          <t>+3.59% (Artış)</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>+2.89% (Artış)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Küresel Dolar</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4.03</v>
+        <v>4.8</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1963,37 +1963,37 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>+0.30% (Artış)</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>+3.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>+14.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>-2.10% (Azalış)</t>
+          <t>+0.78% (Artış)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-1.92% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>-4.38% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>+9.28% (Artış)</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>+4.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>-16.20% (Azalış)</t>
+          <t>+29.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>+33.58% (Artış)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>ABD Hazine</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4.21</v>
+        <v>4.99</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -2023,37 +2023,37 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>+0.45% (Artış)</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>+3.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>+12.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>-0.80% (Azalış)</t>
+          <t>+0.71% (Artış)</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>-2.16% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>-3.37% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>+7.48% (Artış)</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>+8.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>-13.40% (Azalış)</t>
+          <t>+19.82% (Artış)</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>+24.98% (Artış)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>ABD Gösterge</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4.5</v>
+        <v>5.32</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -2083,37 +2083,37 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>+0.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>+2.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>+9.80% (Artış)</t>
+          <t>+0.53% (Artış)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-2.23% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>-2.67% (Azalış)</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>+0.90% (Artış)</t>
+          <t>+3.71% (Artış)</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>+11.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>-9.80% (Azalış)</t>
+          <t>+9.81% (Artış)</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>+16.23% (Artış)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>ABD Uzun Vade</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
     </row>
@@ -2133,47 +2133,45 @@
           <t>Türkiye 2 Yıllık Tahvil</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>42.65</v>
-      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>-0.15% (Azalış)</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>-0.45% (Azalış)</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>+1.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>+7.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>+14.80% (Artış)</t>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>TR Gösterge</t>
+          <t>Tahvil / CDS Piyasası</t>
         </is>
       </c>
     </row>
@@ -2193,9 +2191,7 @@
           <t>Türkiye 10 Yıllık Tahvil</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>29.8</v>
-      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>%</t>
@@ -2203,37 +2199,37 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>-0.10% (Yatay)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>-0.80% (Azalış)</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>+3.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>+5.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>+11.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>+8.90% (Artış)</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>TR Uzun Vade</t>
+          <t>Tahvil / CDS Piyasası</t>
         </is>
       </c>
     </row>
@@ -2253,47 +2249,45 @@
           <t>Türkiye 5 Yıllık CDS</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>266.5</v>
-      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>bp</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>-0.56% (Azalış)</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>-1.80% (Azalış)</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>-3.40% (Azalış)</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>+1.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>-5.80% (Azalış)</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>-34.20% (Azalış)</t>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Ülke Risk Primi</t>
+          <t>Tahvil / CDS Piyasası</t>
         </is>
       </c>
     </row>
@@ -2314,41 +2308,41 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>116.72</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>-0.65% (Azalış)</t>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>+3.14% (Artış)</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>+2.40% (Artış)</t>
+          <t>+6.24% (Artış)</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>+1.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>-7.80% (Azalış)</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>-2.80% (Azalış)</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>-15.40% (Azalış)</t>
+          <t>+9.49% (Artış)</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>+32.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>+91.82% (Artış)</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>+77.01% (Artış)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2374,41 +2368,41 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>71.15000000000001</v>
+        <v>103.27</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>-0.63% (Azalış)</t>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+3.82% (Artış)</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>+2.75% (Artış)</t>
+          <t>+1.83% (Artış)</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>+1.95% (Artış)</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>-8.40% (Azalış)</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>-0.70% (Yatay)</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>-14.80% (Azalış)</t>
+          <t>+9.15% (Artış)</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>+25.01% (Artış)</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>+79.85% (Artış)</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>+67.92% (Artış)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2434,41 +2428,41 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+2.44% (Artış)</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>+11.50% (Artış)</t>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>-5.58% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>-15.28% (Azalış)</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>-8.20% (Azalış)</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>+18.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>+0.40% (Yatay)</t>
+          <t>-19.93% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>-4.59% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>-28.38% (Azalış)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>-16.20% (Azalış)</t>
+          <t>-20.10% (Azalış)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2494,7 +2488,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4.38</v>
+        <v>6.48</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -2503,32 +2497,32 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>+0.69% (Artış)</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>+0.45% (Artış)</t>
+          <t>+1.78% (Artış)</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>-0.84% (Azalış)</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>-2.10% (Azalış)</t>
+          <t>-3.61% (Azalış)</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>+6.40% (Artış)</t>
+          <t>+2.16% (Artış)</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>+12.60% (Artış)</t>
+          <t>+15.03% (Artış)</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>+21.80% (Artış)</t>
+          <t>+27.14% (Artış)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2554,41 +2548,41 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>572.5</v>
+        <v>625</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>cent</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>-0.95% (Azalış)</t>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>+0.04% (Yatay)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>-2.80% (Azalış)</t>
+          <t>-5.37% (Azalış)</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>-1.40% (Azalış)</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>+4.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>-8.90% (Azalış)</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>-1.20% (Azalış)</t>
+          <t>-11.60% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>-5.30% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>+23.27% (Artış)</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>+21.95% (Artış)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2614,7 +2608,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>248.4</v>
+        <v>307.45</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -2623,32 +2617,32 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>-1.11% (Azalış)</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>-3.10% (Azalış)</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>-6.80% (Azalış)</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>+6.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>+31.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>+49.50% (Artış)</t>
+          <t>-1.60% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>+0.61% (Artış)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>+11.66% (Artış)</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>-5.27% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>-11.84% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>-23.71% (Azalış)</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2674,16 +2668,16 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3018.45</v>
+        <v>6402.74</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>TL</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+0.97% (Artış)</t>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>-1.38% (Azalış)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2734,26 +2728,26 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Kat</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>-0.30% (Azalış)</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>-4.40% (Azalış)</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>-5.01% (Azalış)</t>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>+0.65% (Artış)</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>+1.72% (Artış)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>+10.17% (Artış)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2761,19 +2755,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>-5.95% (Azalış)</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>+20.55% (Artış)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>-5.58% (Azalış)</t>
+          <t>-12.76% (Azalış)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Altın/Gümüş oranı 80,90 seviyesinde; son 1 ayda gümüşün altına kıyasla daha hızlı yükselmesiyle rasyo %5,01 geriledi.</t>
+          <t>Altın/Gümüş oranı 74.62 ile dengeli bantta seyrediyor.</t>
         </is>
       </c>
     </row>
@@ -2837,11 +2831,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>282.54</v>
+        <v>223.73</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>TL: 9685.4 / Kur: 34.28</t>
+          <t>TL: 11117.0 / Kur: 49.69</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2863,7 +2857,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>%1.3</t>
+          <t>%-0.84</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2873,7 +2867,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Artış</t>
+          <t>Azalış</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2884,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>%3.52</t>
+          <t>%-5.48</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2900,7 +2894,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Artış</t>
+          <t>Azalış</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2911,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>%-2.45</t>
+          <t>%-15.03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2944,7 +2938,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>%-13.8</t>
+          <t>%-22.55</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2971,7 +2965,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>%11.4</t>
+          <t>%-14.67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2981,7 +2975,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Artış</t>
+          <t>Azalış</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2992,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>%1.85</t>
+          <t>%-11.36</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3008,7 +3002,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Artış</t>
+          <t>Azalış</t>
         </is>
       </c>
     </row>
@@ -3024,16 +3018,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>344.2</v>
+        <v>333.44</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Zirveden %-17.91 aşağıda</t>
+          <t>Zirveden %-32.9 aşağıda</t>
         </is>
       </c>
     </row>
@@ -3049,16 +3043,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>254.8</v>
+        <v>223.73</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Dipten +%10.89 yukarıda</t>
+          <t>Dipten +%0.0 yukarıda</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3069,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>%31.0</t>
+          <t>%0.0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3101,7 +3095,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>327.8</v>
+        <v>305.07</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -3110,7 +3104,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tavana uzaklık: %-13.81</t>
+          <t>Tavana uzaklık: %-26.66</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3120,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>261.4</v>
+        <v>223.73</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -3135,7 +3129,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tabandan uzaklık: +%8.09</t>
+          <t>Tabandan uzaklık: +%0.0</t>
         </is>
       </c>
     </row>
@@ -3151,16 +3145,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>298.6</v>
+        <v>299.16</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Uzaklık: %-5.38</t>
+          <t>Uzaklık: %-25.21</t>
         </is>
       </c>
     </row>
@@ -3176,16 +3170,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>261.4</v>
+        <v>243.68</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Uzaklık: +%8.09</t>
+          <t>Uzaklık: +%-8.19</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3195,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>288.95</v>
+        <v>265.64</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -3226,7 +3220,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>299.5</v>
+        <v>278.58</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -3251,7 +3245,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>310.05</v>
+        <v>291.53</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -3276,7 +3270,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>289.4</v>
+        <v>271.17</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -3301,7 +3295,7 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>296.8</v>
+        <v>296.06</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -3326,7 +3320,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>44.6</v>
+        <v>25.5</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -3335,7 +3329,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>BIST 100 Dolar bazında 282,54$ seviyesinde olup 1 yıllık dolar kanalının alt (ucuz/destek) bölgesinde (%31,0) yer alıyor. 52 haftalık zirvesinden (344,20$) %17,9 aşağıda, 52 haftalık dibinden (254,80$) ise %10,9 yukarıda bulunuyor. Son yerel Swing tabanı olan 261,40$ desteğinden %8,1 tepki veren endekste ilk kritik direnç Fibonacci %61,8 (288,95$) ve 200 günlük ortalama (296,80$) bölgesidir.</t>
+          <t>BIST 100 Dolar bazında 223.73$ seviyesinde olup 1 yıllık dolar kanalının alt (ucuz/destek) bölgesinde (%0.0) yer alıyor. 52 haftalık zirvesinden (333.44$) %32.9 aşağıda, 52 haftalık dibinden (223.73$) ise %0.0 yukarıda bulunuyor. Endeks 200 günlük dolar ortalamasının (296.06$) altında baskı altında seyrederken RSI(14) göstergesi 25.5 seviyesindedir.</t>
         </is>
       </c>
     </row>
@@ -3350,19 +3344,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3414,1356 +3408,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>1 Yıl %</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Gün</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>TI2</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Teknoloji Ağırlıklı Sınırlamalı Endeks Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Teknoloji &amp; Yerli Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>+3.42% (Artış)</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>+6.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>+4.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>+48.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>+62.40% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Gün</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>TAU</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>+2.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>+5.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>+2.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>+64.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>+78.10% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Gün</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>GUM</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>+7.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>+12.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>+52.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>+66.80% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Gün</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>YHZ</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Yapı Kredi Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+2.32% (Artış)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>+5.75% (Artış)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>+1.95% (Artış)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>+63.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>+76.90% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Hafta</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>GUM</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>+7.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>+12.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>+52.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>+66.80% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Hafta</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>GTZ</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Garanti Portföy Gümüş Fon Sepeti Fonu</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+2.15% (Artış)</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>+7.45% (Artış)</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>+11.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>+50.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>+64.90% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Hafta</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>TI2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Teknoloji Ağırlıklı Sınırlamalı Endeks Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Teknoloji &amp; Yerli Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+3.42% (Artış)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>+6.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>+4.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>+48.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>+62.40% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Hafta</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>TAU</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+2.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>+5.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>+2.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>+64.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>+78.10% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Ay</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>GUM</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>+7.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>+12.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>+52.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>+66.80% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Ay</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>KZL</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Kuveyt Türk Portföy Altın Katılım Fonu</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+0.95% (Artış)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>+3.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>+8.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>+49.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>+64.20% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Ay</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>AFT</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Ak Portföy Yeni Teknolojiler Yabancı Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Teknoloji &amp; Yabancı Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+0.94% (Artış)</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>+7.15% (Artış)</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>+44.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>+58.90% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Ay</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>YAY</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Yapı Kredi Portföy Yabancı Teknoloji Sektörü Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Teknoloji &amp; Yabancı Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+0.88% (Artış)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>+2.25% (Artış)</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>+6.95% (Artış)</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>+45.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>+60.40% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Yılbaşından İtibaren (YTD)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>IIH</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Portföy Üçüncü Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+1.65% (Artış)</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>+3.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>+68.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>+84.50% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Yılbaşından İtibaren (YTD)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>TAU</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+2.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>+5.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>+2.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>+64.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>+78.10% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Yılbaşından İtibaren (YTD)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Marmara Capital Portföy Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+1.38% (Artış)</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>+3.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>+1.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>+56.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>+71.40% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Yılbaşından İtibaren (YTD)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>GUM</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>+7.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>+12.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>+52.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>+66.80% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Yıl</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>IIH</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Portföy Üçüncü Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+1.65% (Artış)</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>+3.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>+68.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>+84.50% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Yıl</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>TAU</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+2.85% (Artış)</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>+5.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>+2.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>+64.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>+78.10% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Yıl</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Marmara Capital Portföy Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+1.38% (Artış)</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>+3.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>+1.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>+56.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>+71.40% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Son 1 Yıl</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>GUM</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>+7.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>+12.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>+52.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>+66.80% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Takip Listesi</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>TI2</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Teknoloji Ağırlıklı Sınırlamalı Endeks Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Teknoloji &amp; Yerli Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+3.42% (Artış)</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>+6.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>+4.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>+48.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>+62.40% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Takip Listesi</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>TTE</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>İş Portföy BIST Teknoloji Endeksi Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Teknoloji &amp; Yerli Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+2.95% (Artış)</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>+5.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>+3.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>+41.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>+54.80% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Takip Listesi</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>MAC</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Marmara Capital Portföy Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+1.38% (Artış)</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>+3.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>+1.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>+56.20% (Artış)</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>+71.40% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Takip Listesi</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>IPB</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Portföy Birinci Değişken Fon</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Değişken / Aktif Dağılım Kapsamı</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+0.88% (Artış)</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>+3.50% (Artış)</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>+46.80% (Artış)</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>+61.20% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Takip Listesi</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>AFT</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Ak Portföy Yeni Teknolojiler Yabancı Hisse Senedi Fonu</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Teknoloji &amp; Yabancı Hisse Kapsamı</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+0.94% (Artış)</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>+2.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>+7.15% (Artış)</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>+44.60% (Artış)</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>+58.90% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Takip Listesi</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>KZL</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Kuveyt Türk Portföy Altın Katılım Fonu</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+0.95% (Artış)</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>+3.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>+8.90% (Artış)</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>+49.40% (Artış)</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>+64.20% (Artış)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Takip Listesi</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>PPN</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Nurol Portföy Para Piyasası Fonu</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Para Piyasası &amp; Kısa Vadeli Likidite Kapsamı</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+0.14% (Artış)</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>+0.98% (Artış)</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>+4.18% (Artış)</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>+44.10% (Artış)</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>+55.60% (Artış)</t>
         </is>
       </c>
     </row>
@@ -4778,18 +3422,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4842,22 +3486,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bugün Açıklananlar</t>
+          <t>Bu Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Türkiye (TCMB/TÜİK)</t>
+          <t>Türkiye (TCMB)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4867,138 +3511,138 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>TCMB Piyasa Katılımcıları Anketi ve Enflasyon Beklentileri</t>
+          <t>TCMB Haftalık Uluslararası Rezervler ve Yabancı Menkul Kıymet İstatistikleri</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>%43,11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>%43,50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>%43,14</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Bugün Açıklananlar</t>
+          <t>Bu Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Türkiye (TCMB)</t>
+          <t>Türkiye (TÜİK)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Yüksek</t>
+          <t>Orta</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>TCMB Para Politikası Kurulu (PPK) Faiz Kararı Özeti</t>
+          <t>TÜİK Ekonomik Güven Endeksi ve Dış Ticaret Dengesi</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>%50,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>%50,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>%50,00</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Bugün Açıklananlar</t>
+          <t>Bu Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ABD (Fed/Makro)</t>
+          <t>Türkiye (TÜİK)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Yüksek</t>
+          <t>Orta</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı Mal Siparişleri (Aylık)</t>
+          <t>TÜİK Ekonomik Güven Endeksi ve Dış Ticaret Dengesi</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bugün Açıklananlar</t>
+          <t>Gelecek Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ABD (Fed/Makro)</t>
+          <t>Türkiye (TÜİK)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5008,34 +3652,34 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Michigan Tüketici Güven Endeksi ve Enflasyon Beklentisi</t>
+          <t>TÜİK Aylık ve Yıllık TÜFE (Enflasyon) Verileri</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bu Hafta Açıklanacaklar</t>
+          <t>Gelecek Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5045,17 +3689,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Türkiye (TCMB)</t>
+          <t>Türkiye (TÜİK)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Orta</t>
+          <t>Yüksek</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Reel Kesim Güven Endeksi ve İmalat Sanayi Kapasite Kullanım Oranı</t>
+          <t>TÜİK Aylık ve Yıllık TÜFE (Enflasyon) Verileri</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5065,34 +3709,34 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Bu Hafta Açıklanacaklar</t>
+          <t>Gelecek Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ABD (Fed/Makro)</t>
+          <t>Türkiye (TCMB)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5102,7 +3746,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Haftalık İşsizlik Maaşı Başvuruları</t>
+          <t>TCMB Haftalık Uluslararası Rezervler ve Yabancı Menkul Kıymet İstatistikleri</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5112,341 +3756,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>240K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>227K</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Bu Hafta Açıklanacaklar</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ABD (Fed/Makro)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Yüksek</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Öncü İmalat ve Hizmetler PMI Verileri</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ABD (Fed/Makro)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Yüksek</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>ABD 3. Çeyrek Öncü GSYH Büyüme Oranı (Çeyreklik)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>%3,0</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>%3,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Türkiye (TÜİK)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Orta</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>TÜİK Dış Ticaret Dengesi ve Ekonomik Güven Endeksi</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Türkiye (TCMB)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Yüksek</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>TCMB Haftalık Döviz Rezervleri ve Yabancı Menkul Kıymet İstatistikleri</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>ABD (Fed/Makro)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Yüksek</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Fed'in Favori Enflasyon Göstergesi: Çekirdek PCE Fiyat Endeksi</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>%0,3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>%0,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>ABD (Fed/Makro)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Yüksek</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>ABD Tarım Dışı İstihdam (NFP) ve İşsizlik Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>115K / %4,1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>254K / %4,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Türkiye (TÜİK)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Yüksek</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>TÜİK Ekim Ayı TÜFE ve ÜFE Enflasyon Verileri</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>%2,45</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>%2,97</t>
         </is>
       </c>
     </row>
@@ -5461,13 +3776,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="75" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5505,12 +3820,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P 500 zirveye yakın seyrederken yatırımcı iştahı 'Açgözlülük' (Greed) bölgesinde güçlü kalmaya devam ediyor.</t>
+          <t>S&amp;P 500 fiyat momentumu, VIX volatilitesi ve piyasa genişliği bazlı duyarlılık.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>68/100 (Açgözlülük)</t>
+          <t>21/100 (Aşırı Korku)</t>
         </is>
       </c>
     </row>
@@ -5527,12 +3842,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Merkez bankası alımları ve jeopolitik güvenli liman talebiyle altında 'Aşırı Açgözlülük' (Extreme Greed) momentumu hakim.</t>
+          <t>Ons Altın RSI(14), 50/200 günlük ortalama sapması ve güvenli liman talebi endeksi.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>76/100 (Aşırı Açgözlülük)</t>
+          <t>26/100 (Korku)</t>
         </is>
       </c>
     </row>
@@ -5549,12 +3864,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bitcoin'in 68 bin dolar üzerinde tutunması ve ETF girişleriyle kripto duyarlılığı 'Açgözlülük' bölgesinde.</t>
+          <t>Alternative.me kripto volatilite, hacim ve sosyal duyarlılık endeksi.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72/100 (Açgözlülük)</t>
+          <t>51/100 (Nötr)</t>
         </is>
       </c>
     </row>
@@ -5566,17 +3881,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Bloomberg HT</t>
+          <t>BBC</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>TCMB Başkanı Karahan: Dezenflasyon sürecinde hizmet enflasyonundaki katılığın zayıflamasını yakından izliyoruz</t>
+          <t>Merkez Bankası'nın faizi %36'ya indirme kararı nasıl yorumlandı?</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>TCMB, Karahan, Enflasyon</t>
+          <t>Merkez Bankası, Faiz</t>
         </is>
       </c>
     </row>
@@ -5588,17 +3903,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ekonomim</t>
+          <t>TRT Haber</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs ve Morgan Stanley, Türkiye için yıl sonu politika faizi ve enflasyon patikası tahminlerini güncelledi</t>
+          <t>Merkez Bankası faiz kararını açıkladı</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs, Morgan Stanley, Faiz</t>
+          <t>Merkez Bankası, Faiz</t>
         </is>
       </c>
     </row>
@@ -5610,17 +3925,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Dünya Gazetesi</t>
+          <t>Investing.com Türkiye</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BofA (Bank of America) Raporu: Türk tahvillerine ve bankacılık hisselerine yabancı ilgisi devam ediyor</t>
+          <t>TCMB Faiz Kararını Bugün Açıklıyor: Beklentiler ve Piyasa Senaryoları</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>BofA, Tahvil</t>
+          <t>TCMB, Faiz</t>
         </is>
       </c>
     </row>
@@ -5632,17 +3947,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CNBC-e</t>
+          <t>Uzmanpara</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Fed yetkililerinden faiz indirimi mesajı: İstihdam piyasası dengelenirken kademeli gevşeme sürecek</t>
+          <t>Son dakika...Merkez Bankası faiz kararını açıklayacak! İşte piyasanın tahmini</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Fed, Faiz</t>
+          <t>Merkez Bankası, Faiz</t>
         </is>
       </c>
     </row>
@@ -5654,103 +3969,213 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Anadolu Ajansı</t>
+          <t>DW.com</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Hazine ve Maliye Bakanı Mehmet Şimşek: Cari açıktaki düşüş ve rezerv birikimi makro finansal istikrarı güçlendiriyor</t>
+          <t>Merkez Bankası'nın faiz indirimi işe yarayacak mı?</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Hazine, Şimşek, Rezerv</t>
+          <t>Merkez Bankası, Faiz</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TÜİK Konut İstatistikleri</t>
+          <t>Otorite / Banka Açıklaması</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TÜİK / Bloomberg HT</t>
+          <t>Bloomberght</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TÜİK Konut Satış İstatistikleri: Türkiye genelinde konut satışları bir önceki yılın aynı ayına göre %37,3 artarak 140 bin 919 oldu</t>
+          <t>Fitch'ten Türk leasing ve faktoring şirketleri için varlık uyarısı</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Konut İstatistikleri, TÜİK</t>
+          <t>Fitch</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TÜİK Konut İstatistikleri</t>
+          <t>Otorite / Banka Açıklaması</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TÜİK / Ekonomim</t>
+          <t>Habertürk</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>İpotekli konut satışları yıllık bazda %60,3 artış gösterirken toplam satışlar içindeki payı %11,2 olarak gerçekleşti</t>
+          <t>JPMorgan, Türkiye'deki bankacılık faaliyetlerini büyütme kararı aldığını açıkladı</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Konut İstatistikleri, TÜİK</t>
+          <t>JPMorgan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ODMD Araç İstatistikleri</t>
+          <t>Otorite / Banka Açıklaması</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ODMD / Otomotiv Sektörü</t>
+          <t>Uzmanpara</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ODMD Verileri: Türkiye otomobil ve hafif ticari araç toplam pazarı Ocak-Eylül döneminde 849 bin 892 adet seviyesinde gerçekleşti</t>
+          <t>EKİM 2026 FED FAİZ KARARI NE ZAMAN AÇIKLANACAK? Amerikan Merkez Bankası (FED) faiz beklentisi ne yönde? FED Ekim ayı toplantı tarihleri...</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Otomotiv Pazarı, ODMD</t>
+          <t>Merkez Bankası, Fed, Faiz</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Otorite / Banka Açıklaması</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CNN Türk</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FED FAİZ KARARI NE ZAMAN, BU HAFTA MI? FED Ekim Ayı Faiz Kararı Toplantı Tarihi 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Fed, Faiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Otorite / Banka Açıklaması</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Foreks.com</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Fed'in faiz kararı öncesi altın fiyatları üzerinde baskı sürüyor</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Fed, Faiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TÜİK Konut İstatistikleri</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Amida Haber</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>TÜİK konut satış istatistiklerini açıkladı: Dikkat çekici düşüş</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Konut İstatistikleri, TÜİK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TÜİK Konut İstatistikleri</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Gazete Merhaba</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Balıkesir'de Eylül'de 3 Bin Konut Satıldı</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Konut İstatistikleri, TÜİK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>ODMD Araç İstatistikleri</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>ODMD / Dünya</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Otomobil satışlarında elektrikli ve hibrit araçların toplam pazar payı %25 sınırını aştı</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Foreks.com</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>ODMD: Otomobil ve hafif ticari araç pazarı eylülde yüzde 24,3 daraldı</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Otomotiv Pazarı, ODMD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ODMD Araç İstatistikleri</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberght</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Eylül'de otomotiv satışlarında sert fren</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Otomotiv Pazarı, ODMD</t>
         </is>

--- a/raporlar/2026-10-24/2026-10-24_finans_tablosu.xlsx
+++ b/raporlar/2026-10-24/2026-10-24_finans_tablosu.xlsx
@@ -778,28 +778,28 @@
         <v>4.99</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>42.65</v>
+        <v>38.45</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>29.8</v>
+        <v>28.15</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>266.5</v>
+        <v>258.4</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>80390.37</v>
+        <v>80420.42999999999</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>2335.29</v>
+        <v>2337.31</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AA2" s="2" t="n">
         <v>2.71</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>59.57</v>
+        <v>59.56</v>
       </c>
       <c r="AC2" s="2" t="n">
         <v>116.72</v>
@@ -818,12 +818,12 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TI2 (%2.42)</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IIH (%74.5)</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + TradingView (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + TradingView (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + TradingView (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>80390.37</v>
+        <v>80420.42999999999</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -1543,37 +1543,37 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>-0.84% (Azalış)</t>
+          <t>-0.81% (Azalış)</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>-1.79% (Azalış)</t>
+          <t>-1.75% (Azalış)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>-5.16% (Azalış)</t>
+          <t>-5.12% (Azalış)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>+4.29% (Artış)</t>
+          <t>+4.33% (Artış)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>-8.13% (Azalış)</t>
+          <t>-8.10% (Azalış)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>-27.60% (Azalış)</t>
+          <t>-27.57% (Azalış)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + Binance (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2335.29</v>
+        <v>2337.31</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -1603,37 +1603,37 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>-2.05% (Azalış)</t>
+          <t>-1.96% (Azalış)</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-2.89% (Azalış)</t>
+          <t>-2.81% (Azalış)</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>-13.10% (Azalış)</t>
+          <t>-13.02% (Azalış)</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>-3.67% (Azalış)</t>
+          <t>-3.59% (Azalış)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>-21.29% (Azalış)</t>
+          <t>-21.22% (Azalış)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>-40.65% (Azalış)</t>
+          <t>-40.60% (Azalış)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + Binance (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1663,37 +1663,37 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>-0.71% (Azalış)</t>
+          <t>-0.52% (Azalış)</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>-1.38% (Azalış)</t>
+          <t>-1.19% (Azalış)</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>-13.58% (Azalış)</t>
+          <t>-13.41% (Azalış)</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>-12.23% (Azalış)</t>
+          <t>-12.06% (Azalış)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>-30.18% (Azalış)</t>
+          <t>-30.04% (Azalış)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>-48.77% (Azalış)</t>
+          <t>-48.67% (Azalış)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + Binance (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + ER-API (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + ER-API (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo + ER-API (✓ Doğrulandı)</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Yahoo Finance (Birincil)</t>
         </is>
       </c>
     </row>
@@ -2133,40 +2133,42 @@
           <t>Türkiye 2 Yıllık Tahvil</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>38.45</v>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>-0.25% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-0.80% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>-2.40% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>-4.10% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>-6.50% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>-8.20% (Azalış)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2191,40 +2193,42 @@
           <t>Türkiye 10 Yıllık Tahvil</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>28.15</v>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>-0.15% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>-0.45% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>-1.20% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>-2.30% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>-3.10% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>-4.50% (Azalış)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2249,40 +2253,42 @@
           <t>Türkiye 5 Yıllık CDS</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>258.4</v>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>bp</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>-0.40% (Azalış)</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-1.60% (Azalış)</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>-3.20% (Azalış)</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>-4.80% (Azalış)</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>-8.40% (Azalış)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>-18.50% (Azalış)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3344,19 +3350,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3408,6 +3414,1356 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>1 Yıl %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Gün</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>TI2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Teknoloji Ağırlıklı Sınırlamalı Endeks Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>+2.42% (Artış)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>+5.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>+44.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>+59.40% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Gün</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Teknoloji Endeksi Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>+2.15% (Artış)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>+4.65% (Artış)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>+5.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>+39.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>+52.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Gün</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>GUM</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>+1.95% (Artış)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>+11.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>+49.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>+63.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Gün</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>TAU</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>+1.85% (Artış)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>+4.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>+3.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>+54.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>+68.10% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Hafta</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>GUM</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+1.95% (Artış)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>+11.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>+49.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>+63.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Hafta</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>TI2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Teknoloji Ağırlıklı Sınırlamalı Endeks Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>+2.42% (Artış)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>+5.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>+44.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>+59.40% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Hafta</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TAU</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+1.85% (Artış)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>+4.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>+3.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>+54.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>+68.10% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Hafta</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Teknoloji Endeksi Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+2.15% (Artış)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>+4.65% (Artış)</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>+5.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>+39.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>+52.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Ay</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>GUM</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+1.95% (Artış)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>+11.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>+49.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>+63.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Ay</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>KZL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk Portföy Altın Katılım Fonu</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>+0.95% (Artış)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>+3.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>+8.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>+47.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>+61.20% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Ay</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>AFT</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Ak Portföy Yeni Teknolojiler Yabancı Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Yabancı Hisse / Küresel Piyasalar Kapsamı</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+1.34% (Artış)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>+3.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>+7.45% (Artış)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>+42.60% (Artış)</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>+56.90% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Ay</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>YAY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Yapı Kredi Portföy Yabancı Teknoloji Sektörü Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Yabancı Hisse / Küresel Piyasalar Kapsamı</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>+1.28% (Artış)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>+3.05% (Artış)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>+7.15% (Artış)</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>+43.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>+58.40% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Yılbaşından İtibaren (YTD)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>IIH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Portföy Üçüncü Hisse Senedi Fonu (Hisse Yoğun)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>+1.15% (Artış)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>+3.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>+4.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>+58.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>+74.50% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Yılbaşından İtibaren (YTD)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>TAU</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+1.85% (Artış)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>+4.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>+3.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>+54.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>+68.10% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Yılbaşından İtibaren (YTD)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Marmara Capital Portföy Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+0.98% (Artış)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>+2.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>+2.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>+51.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>+66.40% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Yılbaşından İtibaren (YTD)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>GUM</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+1.95% (Artış)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>+11.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>+49.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>+63.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Yıl</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>IIH</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Portföy Üçüncü Hisse Senedi Fonu (Hisse Yoğun)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>+1.15% (Artış)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>+3.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>+4.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>+58.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>+74.50% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Yıl</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>TAU</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Banka Endeksi Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Bankacılık &amp; Finans Sektörü Hisse Kapsamı</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>+1.85% (Artış)</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>+4.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>+3.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>+54.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>+68.10% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Yıl</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Marmara Capital Portföy Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Yerli Hisse Senedi (BIST) Kapsamı</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>+0.98% (Artış)</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>+2.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>+2.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>+51.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>+66.40% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Son 1 Yıl</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>GUM</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Ak Portföy Gümüş Fon Sepeti Fonu</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Altın &amp; Kıymetli Madenler Kapsamı</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>+1.95% (Artış)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>+11.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>+49.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>+63.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Takip Listesi</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TI2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Teknoloji Ağırlıklı Sınırlamalı Endeks Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Hisse Senedi Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>+2.42% (Artış)</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>+5.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>+6.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>+44.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>+59.40% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Takip Listesi</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>İş Portföy BIST Teknoloji Endeksi Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Hisse Senedi Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>+2.15% (Artış)</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>+4.65% (Artış)</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>+5.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>+39.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>+52.80% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Takip Listesi</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Marmara Capital Portföy Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Hisse Senedi Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+0.98% (Artış)</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>+2.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>+2.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>+51.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>+66.40% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Takip Listesi</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>IPB</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Portföy Birinci Değişken Fon</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Değişken Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>+0.88% (Artış)</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>+2.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>+3.50% (Artış)</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>+45.80% (Artış)</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>+60.20% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Takip Listesi</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>AFT</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Ak Portföy Yeni Teknolojiler Yabancı Hisse Senedi Fonu</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Hisse Senedi Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+1.34% (Artış)</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>+3.20% (Artış)</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>+7.45% (Artış)</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>+42.60% (Artış)</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>+56.90% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Takip Listesi</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>KZL</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Kuveyt Türk Portföy Altın Katılım Fonu</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Katılım Şemsiye Fonu (Altın)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>+0.95% (Artış)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>+3.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>+8.90% (Artış)</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>+47.40% (Artış)</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>+61.20% (Artış)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Takip Listesi</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>PPN</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Nurol Portföy Para Piyasası Fonu</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Para Piyasası Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+0.14% (Artış)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>+0.98% (Artış)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>+4.18% (Artış)</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>+44.10% (Artış)</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>+55.60% (Artış)</t>
         </is>
       </c>
     </row>
@@ -3422,13 +4778,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -3627,22 +4983,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
+          <t>Bu Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Türkiye (TÜİK)</t>
+          <t>ABD (Fed/Makro)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3652,7 +5008,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>TÜİK Aylık ve Yıllık TÜFE (Enflasyon) Verileri</t>
+          <t>Durable Goods Orders MoM</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3662,34 +5018,34 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Gelecek Hafta Açıklanacaklar</t>
+          <t>Bu Hafta Açıklanacaklar</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Türkiye (TÜİK)</t>
+          <t>ABD (Fed/Makro)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3699,7 +5055,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>TÜİK Aylık ve Yıllık TÜFE (Enflasyon) Verileri</t>
+          <t>Fed Interest Rate Decision</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3709,59 +5065,858 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Bu Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Fed Press Conference</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Bu Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Personal Income MoM</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Bu Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Personal Spending MoM</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Bu Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Core PCE Price Index MoM</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Bu Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>GDP Growth Rate QoQ Adv</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Bu Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Euro Bölgesi (ECB)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ECB Interest Rate Decision</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Bu Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Euro Bölgesi (ECB)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Deposit Facility Rate</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Gelecek Hafta Açıklanacaklar</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Türkiye (TÜİK)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>TÜİK Aylık ve Yıllık TÜFE (Enflasyon) Verileri</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Türkiye (TÜİK)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>TÜİK Aylık ve Yıllık TÜFE (Enflasyon) Verileri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>2026-11-05</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Türkiye (TCMB)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Yüksek</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>TCMB Haftalık Uluslararası Rezervler ve Yabancı Menkul Kıymet İstatistikleri</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ISM İmalat PMI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Midterm Elections</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>JOLTs Job Openings</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7.079</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Euro Bölgesi (ECB)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Inflation Rate YoY Flash</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ISM Hizmetler PMI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>İşsizlik Oranı</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Non Farm Payrolls</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Gelecek Hafta Açıklanacaklar</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ABD (Fed/Makro)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Yüksek</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Michigan Consumer Sentiment Prel</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
     </row>
